--- a/jogos_2026-11-07.xlsx
+++ b/jogos_2026-11-07.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G14">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G24">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G38">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G67">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G142">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G144">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G178">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G188">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G197">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G227">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G228">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G247">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G248">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G324">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G325">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G326">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G328">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G330">

--- a/jogos_2026-11-07.xlsx
+++ b/jogos_2026-11-07.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G10">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G23">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G29">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G35">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G38">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G62">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garudayaksa FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Garudayaksa FC</t>
         </is>
       </c>
       <c r="G77">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G144">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.49</v>
+        <v>1.21</v>
       </c>
       <c r="O173">
-        <v>3.8</v>
+        <v>7.75</v>
       </c>
       <c r="P173">
-        <v>2.86</v>
+        <v>16</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,16 +28547,16 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB173">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC173">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD173">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.21</v>
+        <v>2.49</v>
       </c>
       <c r="O174">
-        <v>7.75</v>
+        <v>3.8</v>
       </c>
       <c r="P174">
-        <v>16</v>
+        <v>2.86</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,16 +28710,16 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC174">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD174">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE174">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G178">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G183">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G195">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G197">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G263">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G264">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G305">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G306">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G307">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G308">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G309">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G310">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G319">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G321">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G322">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G323">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G324">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G325">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G326">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G328">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G330">

--- a/jogos_2026-11-07.xlsx
+++ b/jogos_2026-11-07.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G16">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G24">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G38">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G64">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G72">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G86">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G98">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G309">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G310">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G321">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G322">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G330">

--- a/jogos_2026-11-07.xlsx
+++ b/jogos_2026-11-07.xlsx
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>13.83</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49417,10 +49417,10 @@
         <v>0</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE301">
         <v>0</v>

--- a/jogos_2026-11-07.xlsx
+++ b/jogos_2026-11-07.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU331"/>
+  <dimension ref="A1:AU333"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8412,27 +8412,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G50">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-11-07 08:15:00</t>
+          <t>2026-11-07 08:00:00</t>
         </is>
       </c>
     </row>
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G51">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G52">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-11-07 08:30:00</t>
+          <t>2026-11-07 08:15:00</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G54">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-11-07 08:45:00</t>
+          <t>2026-11-07 08:30:00</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-11-07 09:00:00</t>
+          <t>2026-11-07 08:45:00</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G67">
@@ -11351,22 +11351,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garudayaksa FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G77">
@@ -12976,12 +12976,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G78">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-11-07 09:15:00</t>
+          <t>2026-11-07 09:00:00</t>
         </is>
       </c>
     </row>
@@ -13139,27 +13139,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Garudayaksa FC</t>
         </is>
       </c>
       <c r="G79">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N79">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-11-07 09:15:00</t>
+          <t>2026-11-07 09:00:00</t>
         </is>
       </c>
     </row>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="AA80">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC80">
         <v>0</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-11-07 09:30:00</t>
+          <t>2026-11-07 09:15:00</t>
         </is>
       </c>
     </row>
@@ -13465,27 +13465,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G81">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N81">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-11-07 09:30:00</t>
+          <t>2026-11-07 09:15:00</t>
         </is>
       </c>
     </row>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G84">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-11-07 09:45:00</t>
+          <t>2026-11-07 09:30:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-11-07 09:45:00</t>
+          <t>2026-11-07 09:30:00</t>
         </is>
       </c>
     </row>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-11-07 09:55:00</t>
+          <t>2026-11-07 09:45:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-11-07 10:00:00</t>
+          <t>2026-11-07 09:45:00</t>
         </is>
       </c>
     </row>
@@ -14769,27 +14769,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G89">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-11-07 10:00:00</t>
+          <t>2026-11-07 09:55:00</t>
         </is>
       </c>
     </row>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G92">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G105">
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-11-07 10:20:00</t>
+          <t>2026-11-07 10:00:00</t>
         </is>
       </c>
     </row>
@@ -17703,12 +17703,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-11-07 10:30:00</t>
+          <t>2026-11-07 10:00:00</t>
         </is>
       </c>
     </row>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-11-07 10:30:00</t>
+          <t>2026-11-07 10:20:00</t>
         </is>
       </c>
     </row>
@@ -18034,22 +18034,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>5.54</v>
+        <v>0</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G118">
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-11-07 10:45:00</t>
+          <t>2026-11-07 10:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-11-07 10:45:00</t>
+          <t>2026-11-07 10:30:00</t>
         </is>
       </c>
     </row>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G127">
@@ -21126,12 +21126,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G128">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-11-07 11:00:00</t>
+          <t>2026-11-07 10:45:00</t>
         </is>
       </c>
     </row>
@@ -21289,12 +21289,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G129">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-11-07 11:00:00</t>
+          <t>2026-11-07 10:45:00</t>
         </is>
       </c>
     </row>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,22 +22598,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,22 +22761,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G139">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O141">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P141">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O142">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P142">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23902,22 +23902,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,22 +24065,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G147">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G149">
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G153">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G155">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G158">
@@ -26184,7 +26184,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O159">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="P159">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O160">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="P160">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26505,12 +26505,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>2026-11-07 11:15:00</t>
+          <t>2026-11-07 11:00:00</t>
         </is>
       </c>
     </row>
@@ -26668,12 +26668,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26819,7 +26819,7 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>2026-11-07 11:30:00</t>
+          <t>2026-11-07 11:00:00</t>
         </is>
       </c>
     </row>
@@ -26831,12 +26831,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G163">
@@ -26982,7 +26982,7 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>2026-11-07 11:30:00</t>
+          <t>2026-11-07 11:15:00</t>
         </is>
       </c>
     </row>
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G165">
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G166">
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G167">
@@ -27651,7 +27651,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G168">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O169">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="P169">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27901,10 +27901,10 @@
         <v>0</v>
       </c>
       <c r="AC169">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD169">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE169">
         <v>0</v>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O170">
-        <v>6.58</v>
+        <v>0</v>
       </c>
       <c r="P170">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28064,10 +28064,10 @@
         <v>0</v>
       </c>
       <c r="AC170">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD170">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>6.62</v>
+        <v>1.52</v>
       </c>
       <c r="O171">
-        <v>5.9</v>
+        <v>5.39</v>
       </c>
       <c r="P171">
-        <v>1.44</v>
+        <v>5.8</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28227,13 +28227,13 @@
         <v>0</v>
       </c>
       <c r="AC171">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD171">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE171">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.62</v>
+        <v>6.62</v>
       </c>
       <c r="O172">
-        <v>4.11</v>
+        <v>5.9</v>
       </c>
       <c r="P172">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28390,13 +28390,13 @@
         <v>0</v>
       </c>
       <c r="AC172">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD172">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE172">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF172">
         <v>0</v>
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.21</v>
+        <v>2.62</v>
       </c>
       <c r="O173">
-        <v>7.75</v>
+        <v>4.11</v>
       </c>
       <c r="P173">
-        <v>16</v>
+        <v>2.56</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28553,10 +28553,10 @@
         <v>0</v>
       </c>
       <c r="AC173">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD173">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AE173">
         <v>0</v>
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-11-07 12:00:00</t>
+          <t>2026-11-07 11:30:00</t>
         </is>
       </c>
     </row>
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.49</v>
+        <v>1.32</v>
       </c>
       <c r="O174">
-        <v>3.8</v>
+        <v>6.58</v>
       </c>
       <c r="P174">
-        <v>2.86</v>
+        <v>9.5</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,16 +28710,16 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB174">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD174">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE174">
         <v>0</v>
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-11-07 12:00:00</t>
+          <t>2026-11-07 11:30:00</t>
         </is>
       </c>
     </row>
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28879,10 +28879,10 @@
         <v>0</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE175">
         <v>0</v>
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,22 +29444,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,22 +29770,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="O182">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="P182">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30422,22 +30422,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G185">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,22 +30748,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O189">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P189">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G197">
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O198">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P198">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32622,10 +32622,10 @@
         <v>0</v>
       </c>
       <c r="AA198">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC198">
         <v>0</v>
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O199">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P199">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -32785,10 +32785,10 @@
         <v>0</v>
       </c>
       <c r="AA199">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB199">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC199">
         <v>0</v>
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O200">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -32948,10 +32948,10 @@
         <v>0</v>
       </c>
       <c r="AA200">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB200">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC200">
         <v>0</v>
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33111,10 +33111,10 @@
         <v>0</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC201">
         <v>0</v>
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G204">
@@ -33677,12 +33677,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G205">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>2026-11-07 12:15:00</t>
+          <t>2026-11-07 12:00:00</t>
         </is>
       </c>
     </row>
@@ -33840,12 +33840,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G206">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>2026-11-07 12:15:00</t>
+          <t>2026-11-07 12:00:00</t>
         </is>
       </c>
     </row>
@@ -34003,12 +34003,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G207">
@@ -34154,7 +34154,7 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>2026-11-07 12:30:00</t>
+          <t>2026-11-07 12:15:00</t>
         </is>
       </c>
     </row>
@@ -34166,12 +34166,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G208">
@@ -34317,7 +34317,7 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>2026-11-07 12:30:00</t>
+          <t>2026-11-07 12:15:00</t>
         </is>
       </c>
     </row>
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Hatta</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G213">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Hatta</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O218">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P218">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G219">
@@ -36122,12 +36122,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>2026-11-07 12:45:00</t>
+          <t>2026-11-07 12:30:00</t>
         </is>
       </c>
     </row>
@@ -36285,12 +36285,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G221">
@@ -36436,7 +36436,7 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>2026-11-07 13:00:00</t>
+          <t>2026-11-07 12:30:00</t>
         </is>
       </c>
     </row>
@@ -36448,12 +36448,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G222">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>2026-11-07 13:00:00</t>
+          <t>2026-11-07 12:45:00</t>
         </is>
       </c>
     </row>
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O225">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P225">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37105,7 +37105,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37431,7 +37431,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G229">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G232">
@@ -38241,12 +38241,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G233">
@@ -38392,7 +38392,7 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>2026-11-07 13:15:00</t>
+          <t>2026-11-07 13:00:00</t>
         </is>
       </c>
     </row>
@@ -38404,12 +38404,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="O234">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P234">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38555,7 +38555,7 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>2026-11-07 13:15:00</t>
+          <t>2026-11-07 13:00:00</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G235">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>2026-11-07 13:30:00</t>
+          <t>2026-11-07 13:15:00</t>
         </is>
       </c>
     </row>
@@ -38893,12 +38893,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G237">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>2026-11-07 13:30:00</t>
+          <t>2026-11-07 13:15:00</t>
         </is>
       </c>
     </row>
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G238">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,22 +39387,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,22 +39550,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,22 +39713,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G242">
@@ -39876,22 +39876,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G243">
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O244">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="P244">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G248">
@@ -40849,12 +40849,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G249">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>2026-11-07 13:45:00</t>
+          <t>2026-11-07 13:30:00</t>
         </is>
       </c>
     </row>
@@ -41012,12 +41012,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G250">
@@ -41163,7 +41163,7 @@
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>2026-11-07 14:00:00</t>
+          <t>2026-11-07 13:30:00</t>
         </is>
       </c>
     </row>
@@ -41175,12 +41175,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G251">
@@ -41326,7 +41326,7 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>2026-11-07 14:00:00</t>
+          <t>2026-11-07 13:45:00</t>
         </is>
       </c>
     </row>
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G252">
@@ -41506,7 +41506,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G253">
@@ -41669,22 +41669,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,22 +41995,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O259">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P259">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q259">
         <v>0</v>
@@ -42642,12 +42642,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G260">
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-11-07 14:15:00</t>
+          <t>2026-11-07 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42805,12 +42805,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>4.68</v>
+        <v>3.71</v>
       </c>
       <c r="O261">
-        <v>4.37</v>
+        <v>3.61</v>
       </c>
       <c r="P261">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -42891,10 +42891,10 @@
         <v>0</v>
       </c>
       <c r="AA261">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB261">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC261">
         <v>0</v>
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-11-07 14:30:00</t>
+          <t>2026-11-07 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42968,12 +42968,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G262">
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-11-07 14:30:00</t>
+          <t>2026-11-07 14:15:00</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O263">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="P263">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43217,10 +43217,10 @@
         <v>0</v>
       </c>
       <c r="AA263">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB263">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC263">
         <v>0</v>
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G265">
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O265">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P265">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43543,10 +43543,10 @@
         <v>0</v>
       </c>
       <c r="AA265">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB265">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC265">
         <v>0</v>
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G266">
@@ -43788,7 +43788,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="O267">
-        <v>5.49</v>
+        <v>4.2</v>
       </c>
       <c r="P267">
-        <v>6.36</v>
+        <v>6.82</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43869,16 +43869,16 @@
         <v>0</v>
       </c>
       <c r="AA267">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB267">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC267">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD267">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE267">
         <v>0</v>
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-11-07 14:45:00</t>
+          <t>2026-11-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -44201,10 +44201,10 @@
         <v>0</v>
       </c>
       <c r="AC269">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD269">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE269">
         <v>0</v>
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-11-07 14:45:00</t>
+          <t>2026-11-07 14:30:00</t>
         </is>
       </c>
     </row>
@@ -44277,7 +44277,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O270">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P270">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -44358,10 +44358,10 @@
         <v>0</v>
       </c>
       <c r="AA270">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB270">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC270">
         <v>0</v>
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O271">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P271">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44598,12 +44598,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44684,10 +44684,10 @@
         <v>0</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC272">
         <v>0</v>
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-11-07 15:00:00</t>
+          <t>2026-11-07 14:45:00</t>
         </is>
       </c>
     </row>
@@ -44761,27 +44761,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-11-07 15:00:00</t>
+          <t>2026-11-07 14:45:00</t>
         </is>
       </c>
     </row>
@@ -44929,22 +44929,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,22 +45092,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G275">
@@ -45255,22 +45255,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G276">
@@ -45413,12 +45413,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G277">
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>2026-11-07 15:30:00</t>
+          <t>2026-11-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -45576,12 +45576,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O278">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P278">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45727,7 +45727,7 @@
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>2026-11-07 15:30:00</t>
+          <t>2026-11-07 15:00:00</t>
         </is>
       </c>
     </row>
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -46065,27 +46065,27 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G281">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-11-07 16:00:00</t>
+          <t>2026-11-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46228,12 +46228,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G282">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-11-07 16:00:00</t>
+          <t>2026-11-07 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46396,22 +46396,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G283">
@@ -46559,7 +46559,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G284">
@@ -46722,22 +46722,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G285">
@@ -46880,27 +46880,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G286">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-11-07 16:10:00</t>
+          <t>2026-11-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -47043,27 +47043,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G287">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-11-07 16:15:00</t>
+          <t>2026-11-07 16:00:00</t>
         </is>
       </c>
     </row>
@@ -47206,27 +47206,27 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G288">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-11-07 16:30:00</t>
+          <t>2026-11-07 16:10:00</t>
         </is>
       </c>
     </row>
@@ -47369,12 +47369,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G289">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-11-07 16:30:00</t>
+          <t>2026-11-07 16:15:00</t>
         </is>
       </c>
     </row>
@@ -47532,12 +47532,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="O290">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="P290">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-11-07 16:45:00</t>
+          <t>2026-11-07 16:30:00</t>
         </is>
       </c>
     </row>
@@ -47695,12 +47695,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O291">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="P291">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47846,7 +47846,7 @@
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>2026-11-07 16:45:00</t>
+          <t>2026-11-07 16:30:00</t>
         </is>
       </c>
     </row>
@@ -47863,7 +47863,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O292">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P292">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -48026,7 +48026,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O293">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="P293">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="Q293">
         <v>0</v>
@@ -48184,12 +48184,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G294">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-11-07 17:00:00</t>
+          <t>2026-11-07 16:45:00</t>
         </is>
       </c>
     </row>
@@ -48347,12 +48347,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G295">
@@ -48498,7 +48498,7 @@
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>2026-11-07 17:00:00</t>
+          <t>2026-11-07 16:45:00</t>
         </is>
       </c>
     </row>
@@ -48515,7 +48515,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G296">
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G297">
@@ -48841,7 +48841,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O298">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P298">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -49004,7 +49004,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O299">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P299">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49162,27 +49162,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O300">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P300">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-11-07 17:30:00</t>
+          <t>2026-11-07 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49325,12 +49325,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.15</v>
+        <v>2.8</v>
       </c>
       <c r="O301">
-        <v>8.369999999999999</v>
+        <v>3.92</v>
       </c>
       <c r="P301">
-        <v>13.83</v>
+        <v>2.33</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49417,10 +49417,10 @@
         <v>0</v>
       </c>
       <c r="AC301">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AD301">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE301">
         <v>0</v>
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-11-07 17:30:00</t>
+          <t>2026-11-07 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49488,12 +49488,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G302">
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-11-07 18:00:00</t>
+          <t>2026-11-07 17:30:00</t>
         </is>
       </c>
     </row>
@@ -49651,27 +49651,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O303">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="P303">
-        <v>0</v>
+        <v>13.83</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49743,10 +49743,10 @@
         <v>0</v>
       </c>
       <c r="AC303">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD303">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE303">
         <v>0</v>
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-11-07 18:00:00</t>
+          <t>2026-11-07 17:30:00</t>
         </is>
       </c>
     </row>
@@ -49819,7 +49819,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G305">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G306">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G307">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G308">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G309">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G310">
@@ -50955,12 +50955,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G311">
@@ -51106,7 +51106,7 @@
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>2026-11-07 18:15:00</t>
+          <t>2026-11-07 18:00:00</t>
         </is>
       </c>
     </row>
@@ -51118,12 +51118,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G312">
@@ -51269,7 +51269,7 @@
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>2026-11-07 20:00:00</t>
+          <t>2026-11-07 18:00:00</t>
         </is>
       </c>
     </row>
@@ -51281,12 +51281,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G313">
@@ -51432,7 +51432,7 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>2026-11-07 20:00:00</t>
+          <t>2026-11-07 18:15:00</t>
         </is>
       </c>
     </row>
@@ -51444,12 +51444,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G314">
@@ -51595,7 +51595,7 @@
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>2026-11-07 20:30:00</t>
+          <t>2026-11-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -51607,27 +51607,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G315">
@@ -51758,7 +51758,7 @@
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>2026-11-07 21:00:00</t>
+          <t>2026-11-07 20:00:00</t>
         </is>
       </c>
     </row>
@@ -51770,12 +51770,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G316">
@@ -51921,7 +51921,7 @@
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>2026-11-07 21:00:00</t>
+          <t>2026-11-07 20:30:00</t>
         </is>
       </c>
     </row>
@@ -51938,22 +51938,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G319">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G321">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G322">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G323">
@@ -53079,7 +53079,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G324">
@@ -53242,7 +53242,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G325">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G326">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G328">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G330">
@@ -54215,156 +54215,482 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="G331">
+        <v>0</v>
+      </c>
+      <c r="H331">
+        <v>0</v>
+      </c>
+      <c r="I331">
+        <v>0</v>
+      </c>
+      <c r="J331">
+        <v>0</v>
+      </c>
+      <c r="K331">
+        <v>0</v>
+      </c>
+      <c r="L331">
+        <v>0</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N331">
+        <v>0</v>
+      </c>
+      <c r="O331">
+        <v>0</v>
+      </c>
+      <c r="P331">
+        <v>0</v>
+      </c>
+      <c r="Q331">
+        <v>0</v>
+      </c>
+      <c r="R331">
+        <v>0</v>
+      </c>
+      <c r="S331">
+        <v>0</v>
+      </c>
+      <c r="T331">
+        <v>0</v>
+      </c>
+      <c r="U331">
+        <v>0</v>
+      </c>
+      <c r="V331">
+        <v>0</v>
+      </c>
+      <c r="W331">
+        <v>0</v>
+      </c>
+      <c r="X331">
+        <v>0</v>
+      </c>
+      <c r="Y331">
+        <v>0</v>
+      </c>
+      <c r="Z331">
+        <v>0</v>
+      </c>
+      <c r="AA331">
+        <v>0</v>
+      </c>
+      <c r="AB331">
+        <v>0</v>
+      </c>
+      <c r="AC331">
+        <v>0</v>
+      </c>
+      <c r="AD331">
+        <v>0</v>
+      </c>
+      <c r="AE331">
+        <v>0</v>
+      </c>
+      <c r="AF331">
+        <v>0</v>
+      </c>
+      <c r="AG331">
+        <v>0</v>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ331">
+        <v>0</v>
+      </c>
+      <c r="AK331">
+        <v>0</v>
+      </c>
+      <c r="AL331">
+        <v>0</v>
+      </c>
+      <c r="AM331">
+        <v>-1</v>
+      </c>
+      <c r="AN331">
+        <v>-1</v>
+      </c>
+      <c r="AO331">
+        <v>-1</v>
+      </c>
+      <c r="AP331">
+        <v>-1</v>
+      </c>
+      <c r="AQ331">
+        <v>0</v>
+      </c>
+      <c r="AR331">
+        <v>0</v>
+      </c>
+      <c r="AS331">
+        <v>0</v>
+      </c>
+      <c r="AT331">
+        <v>0</v>
+      </c>
+      <c r="AU331" t="inlineStr">
+        <is>
+          <t>2026-11-07 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="G332">
+        <v>0</v>
+      </c>
+      <c r="H332">
+        <v>0</v>
+      </c>
+      <c r="I332">
+        <v>0</v>
+      </c>
+      <c r="J332">
+        <v>0</v>
+      </c>
+      <c r="K332">
+        <v>0</v>
+      </c>
+      <c r="L332">
+        <v>0</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N332">
+        <v>0</v>
+      </c>
+      <c r="O332">
+        <v>0</v>
+      </c>
+      <c r="P332">
+        <v>0</v>
+      </c>
+      <c r="Q332">
+        <v>0</v>
+      </c>
+      <c r="R332">
+        <v>0</v>
+      </c>
+      <c r="S332">
+        <v>0</v>
+      </c>
+      <c r="T332">
+        <v>0</v>
+      </c>
+      <c r="U332">
+        <v>0</v>
+      </c>
+      <c r="V332">
+        <v>0</v>
+      </c>
+      <c r="W332">
+        <v>0</v>
+      </c>
+      <c r="X332">
+        <v>0</v>
+      </c>
+      <c r="Y332">
+        <v>0</v>
+      </c>
+      <c r="Z332">
+        <v>0</v>
+      </c>
+      <c r="AA332">
+        <v>0</v>
+      </c>
+      <c r="AB332">
+        <v>0</v>
+      </c>
+      <c r="AC332">
+        <v>0</v>
+      </c>
+      <c r="AD332">
+        <v>0</v>
+      </c>
+      <c r="AE332">
+        <v>0</v>
+      </c>
+      <c r="AF332">
+        <v>0</v>
+      </c>
+      <c r="AG332">
+        <v>0</v>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI332" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ332">
+        <v>0</v>
+      </c>
+      <c r="AK332">
+        <v>0</v>
+      </c>
+      <c r="AL332">
+        <v>0</v>
+      </c>
+      <c r="AM332">
+        <v>-1</v>
+      </c>
+      <c r="AN332">
+        <v>-1</v>
+      </c>
+      <c r="AO332">
+        <v>-1</v>
+      </c>
+      <c r="AP332">
+        <v>-1</v>
+      </c>
+      <c r="AQ332">
+        <v>0</v>
+      </c>
+      <c r="AR332">
+        <v>0</v>
+      </c>
+      <c r="AS332">
+        <v>0</v>
+      </c>
+      <c r="AT332">
+        <v>0</v>
+      </c>
+      <c r="AU332" t="inlineStr">
+        <is>
+          <t>2026-11-07 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
+      <c r="C333" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
+      <c r="D333" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr">
+      <c r="E333" t="inlineStr">
         <is>
           <t>Náutico</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
+      <c r="F333" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
       </c>
-      <c r="G331">
-        <v>0</v>
-      </c>
-      <c r="H331">
-        <v>0</v>
-      </c>
-      <c r="I331">
-        <v>0</v>
-      </c>
-      <c r="J331">
-        <v>0</v>
-      </c>
-      <c r="K331">
-        <v>0</v>
-      </c>
-      <c r="L331">
-        <v>0</v>
-      </c>
-      <c r="M331" t="inlineStr">
+      <c r="G333">
+        <v>0</v>
+      </c>
+      <c r="H333">
+        <v>0</v>
+      </c>
+      <c r="I333">
+        <v>0</v>
+      </c>
+      <c r="J333">
+        <v>0</v>
+      </c>
+      <c r="K333">
+        <v>0</v>
+      </c>
+      <c r="L333">
+        <v>0</v>
+      </c>
+      <c r="M333" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N331">
-        <v>0</v>
-      </c>
-      <c r="O331">
-        <v>0</v>
-      </c>
-      <c r="P331">
-        <v>0</v>
-      </c>
-      <c r="Q331">
-        <v>0</v>
-      </c>
-      <c r="R331">
-        <v>0</v>
-      </c>
-      <c r="S331">
-        <v>0</v>
-      </c>
-      <c r="T331">
-        <v>0</v>
-      </c>
-      <c r="U331">
-        <v>0</v>
-      </c>
-      <c r="V331">
-        <v>0</v>
-      </c>
-      <c r="W331">
-        <v>0</v>
-      </c>
-      <c r="X331">
-        <v>0</v>
-      </c>
-      <c r="Y331">
-        <v>0</v>
-      </c>
-      <c r="Z331">
-        <v>0</v>
-      </c>
-      <c r="AA331">
-        <v>0</v>
-      </c>
-      <c r="AB331">
-        <v>0</v>
-      </c>
-      <c r="AC331">
-        <v>0</v>
-      </c>
-      <c r="AD331">
-        <v>0</v>
-      </c>
-      <c r="AE331">
-        <v>0</v>
-      </c>
-      <c r="AF331">
-        <v>0</v>
-      </c>
-      <c r="AG331">
-        <v>0</v>
-      </c>
-      <c r="AH331" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI331" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ331">
-        <v>0</v>
-      </c>
-      <c r="AK331">
-        <v>0</v>
-      </c>
-      <c r="AL331">
-        <v>0</v>
-      </c>
-      <c r="AM331">
-        <v>-1</v>
-      </c>
-      <c r="AN331">
-        <v>-1</v>
-      </c>
-      <c r="AO331">
-        <v>-1</v>
-      </c>
-      <c r="AP331">
-        <v>-1</v>
-      </c>
-      <c r="AQ331">
-        <v>0</v>
-      </c>
-      <c r="AR331">
-        <v>0</v>
-      </c>
-      <c r="AS331">
-        <v>0</v>
-      </c>
-      <c r="AT331">
-        <v>0</v>
-      </c>
-      <c r="AU331" t="inlineStr">
+      <c r="N333">
+        <v>0</v>
+      </c>
+      <c r="O333">
+        <v>0</v>
+      </c>
+      <c r="P333">
+        <v>0</v>
+      </c>
+      <c r="Q333">
+        <v>0</v>
+      </c>
+      <c r="R333">
+        <v>0</v>
+      </c>
+      <c r="S333">
+        <v>0</v>
+      </c>
+      <c r="T333">
+        <v>0</v>
+      </c>
+      <c r="U333">
+        <v>0</v>
+      </c>
+      <c r="V333">
+        <v>0</v>
+      </c>
+      <c r="W333">
+        <v>0</v>
+      </c>
+      <c r="X333">
+        <v>0</v>
+      </c>
+      <c r="Y333">
+        <v>0</v>
+      </c>
+      <c r="Z333">
+        <v>0</v>
+      </c>
+      <c r="AA333">
+        <v>0</v>
+      </c>
+      <c r="AB333">
+        <v>0</v>
+      </c>
+      <c r="AC333">
+        <v>0</v>
+      </c>
+      <c r="AD333">
+        <v>0</v>
+      </c>
+      <c r="AE333">
+        <v>0</v>
+      </c>
+      <c r="AF333">
+        <v>0</v>
+      </c>
+      <c r="AG333">
+        <v>0</v>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI333" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ333">
+        <v>0</v>
+      </c>
+      <c r="AK333">
+        <v>0</v>
+      </c>
+      <c r="AL333">
+        <v>0</v>
+      </c>
+      <c r="AM333">
+        <v>-1</v>
+      </c>
+      <c r="AN333">
+        <v>-1</v>
+      </c>
+      <c r="AO333">
+        <v>-1</v>
+      </c>
+      <c r="AP333">
+        <v>-1</v>
+      </c>
+      <c r="AQ333">
+        <v>0</v>
+      </c>
+      <c r="AR333">
+        <v>0</v>
+      </c>
+      <c r="AS333">
+        <v>0</v>
+      </c>
+      <c r="AT333">
+        <v>0</v>
+      </c>
+      <c r="AU333" t="inlineStr">
         <is>
           <t>2026-11-07 21:30:00</t>
         </is>
